--- a/test/fixtures/sample-good.xlsx
+++ b/test/fixtures/sample-good.xlsx
@@ -17,12 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="273">
-  <si>
-    <t>FEMS 수용가 정보</t>
-  </si>
-  <si>
-    <t>회사정보</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="241">
+  <si>
+    <t>사업장 정보</t>
   </si>
   <si>
     <t>* 회사명</t>
@@ -31,16 +28,22 @@
     <t>한빛정밀공업</t>
   </si>
   <si>
+    <t>* 공장코드(접속주소)</t>
+  </si>
+  <si>
+    <t>hanbit</t>
+  </si>
+  <si>
     <t>업종</t>
   </si>
   <si>
     <t>자동차부품제조업</t>
   </si>
   <si>
-    <t>홈페이지 주소</t>
-  </si>
-  <si>
-    <t>http://www.hanbit-example.co.kr/</t>
+    <t>* 주소</t>
+  </si>
+  <si>
+    <t>경기도 안성시 공단로 24</t>
   </si>
   <si>
     <t>* 전화번호</t>
@@ -49,22 +52,37 @@
     <t>031-555-1234</t>
   </si>
   <si>
-    <t>* 주소</t>
-  </si>
-  <si>
-    <t>경기도 안성시 공단로 24</t>
-  </si>
-  <si>
-    <t>신청정보</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> * FEMS 마스터 계정ID</t>
-  </si>
-  <si>
-    <t>hanbit</t>
-  </si>
-  <si>
-    <t>* 공장코드(접속주소)</t>
+    <t>* FEMS 마스터 계정ID</t>
+  </si>
+  <si>
+    <t>담당자</t>
+  </si>
+  <si>
+    <t>* 담당자명</t>
+  </si>
+  <si>
+    <t>이창범</t>
+  </si>
+  <si>
+    <t>직급</t>
+  </si>
+  <si>
+    <t>차장</t>
+  </si>
+  <si>
+    <t>* 휴대전화번호</t>
+  </si>
+  <si>
+    <t>010-2345-6789</t>
+  </si>
+  <si>
+    <t>* 이메일 주소</t>
+  </si>
+  <si>
+    <t>cb.lee@hanbit-example.co.kr</t>
+  </si>
+  <si>
+    <t>수전 계약</t>
   </si>
   <si>
     <t>* 신청 요금제</t>
@@ -73,568 +91,454 @@
     <t>산업용전력(을) - 고압 A - 선택 Ⅱ</t>
   </si>
   <si>
-    <t>한전파워플래너</t>
-  </si>
-  <si>
-    <t>계정</t>
-  </si>
-  <si>
-    <t>0123456789</t>
-  </si>
-  <si>
-    <t>비밀번호</t>
-  </si>
-  <si>
-    <t>kepco-pw-2024</t>
-  </si>
-  <si>
-    <t>수용가 담당자 정보</t>
-  </si>
-  <si>
-    <t>*  담당자명</t>
-  </si>
-  <si>
-    <t>이창범</t>
-  </si>
-  <si>
-    <t>직급</t>
-  </si>
-  <si>
-    <t>차장</t>
-  </si>
-  <si>
-    <t>* 휴대전화번호</t>
-  </si>
-  <si>
-    <t>010-2345-6789</t>
-  </si>
-  <si>
-    <t>* 이메일 주소</t>
-  </si>
-  <si>
-    <t>cb.lee@hanbit-example.co.kr</t>
-  </si>
-  <si>
-    <t>기타</t>
+    <t>* 요금 적용 전력</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>* 수전용량</t>
+  </si>
+  <si>
+    <t>에너지원 (선택)</t>
+  </si>
+  <si>
+    <t>종류</t>
+  </si>
+  <si>
+    <t>전기</t>
+  </si>
+  <si>
+    <t>기본 단위</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>석유환산계수 [toe/단위]</t>
+  </si>
+  <si>
+    <t>탄소배출계수 [tCO2/단위]</t>
+  </si>
+  <si>
+    <t>단가 [원/단위]</t>
+  </si>
+  <si>
+    <t>등록 장비 정보</t>
+  </si>
+  <si>
+    <t>*장비ID</t>
+  </si>
+  <si>
+    <t>*장비 타입</t>
+  </si>
+  <si>
+    <t>* 제품명</t>
+  </si>
+  <si>
+    <t>설치 위치</t>
+  </si>
+  <si>
+    <t>*IP 주소</t>
+  </si>
+  <si>
+    <t>포트</t>
+  </si>
+  <si>
+    <t>전력 채널 수</t>
+  </si>
+  <si>
+    <t>전송주기(초)</t>
+  </si>
+  <si>
+    <t>설치 일자</t>
+  </si>
+  <si>
+    <t>사용여부</t>
+  </si>
+  <si>
+    <t>전력량계</t>
+  </si>
+  <si>
+    <t>Accura 2300</t>
+  </si>
+  <si>
+    <t>1공장 전기실</t>
+  </si>
+  <si>
+    <t>100.100.0.11</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>2공장 전기실</t>
+  </si>
+  <si>
+    <t>100.100.0.12</t>
+  </si>
+  <si>
+    <t>1공장</t>
+  </si>
+  <si>
+    <t>100.100.0.13</t>
+  </si>
+  <si>
+    <t>MPM330a</t>
+  </si>
+  <si>
+    <t>1공장 유틸리티동</t>
+  </si>
+  <si>
+    <t>100.100.0.14</t>
+  </si>
+  <si>
+    <t>2공장</t>
+  </si>
+  <si>
+    <t>100.100.0.15</t>
+  </si>
+  <si>
+    <t>채널정보</t>
+  </si>
+  <si>
+    <t>설비 트리 연동</t>
+  </si>
+  <si>
+    <t>측정부하명</t>
+  </si>
+  <si>
+    <t>설비코드정보</t>
+  </si>
+  <si>
+    <t>설비그룹명</t>
+  </si>
+  <si>
+    <t>설비그룹ID</t>
+  </si>
+  <si>
+    <t>설비명</t>
+  </si>
+  <si>
+    <t>설비ID</t>
+  </si>
+  <si>
+    <t>제1수전 한전메인</t>
+  </si>
+  <si>
+    <t>수배전반</t>
+  </si>
+  <si>
+    <t>제1수전 메인</t>
+  </si>
+  <si>
+    <t>제2수전 한전메인</t>
+  </si>
+  <si>
+    <t>제2수전 메인</t>
+  </si>
+  <si>
+    <t>압출기1호</t>
+  </si>
+  <si>
+    <t>압출기</t>
+  </si>
+  <si>
+    <t>압출기2호</t>
+  </si>
+  <si>
+    <t>압출기 1~2호 통합</t>
+  </si>
+  <si>
+    <t>공압기1호</t>
+  </si>
+  <si>
+    <t>공기압축기</t>
+  </si>
+  <si>
+    <t>A동 공압기</t>
+  </si>
+  <si>
+    <t>공압기2호</t>
+  </si>
+  <si>
+    <t>공압기3호</t>
+  </si>
+  <si>
+    <t>공압기 1~3호 통합</t>
+  </si>
+  <si>
+    <t>사출기1호</t>
+  </si>
+  <si>
+    <t>사출기</t>
+  </si>
+  <si>
+    <t>사출기2호</t>
+  </si>
+  <si>
+    <t>사출기3호</t>
+  </si>
+  <si>
+    <t>사출기4호</t>
+  </si>
+  <si>
+    <t>사출기 1~4호 통합</t>
+  </si>
+  <si>
+    <t>에너지트리정보</t>
+  </si>
+  <si>
+    <t>에너지 포인트연동</t>
+  </si>
+  <si>
+    <t>*에너지원</t>
+  </si>
+  <si>
+    <t>* 계통명</t>
+  </si>
+  <si>
+    <t>*에너지계통 ID</t>
+  </si>
+  <si>
+    <t>계통레벨</t>
+  </si>
+  <si>
+    <t>연결계통ID</t>
+  </si>
+  <si>
+    <t>장비ID</t>
+  </si>
+  <si>
+    <t>압출기 1호기</t>
+  </si>
+  <si>
+    <t>압출기 2호기</t>
+  </si>
+  <si>
+    <t>공기압축기 1호기</t>
+  </si>
+  <si>
+    <t>공기압축기 2호기</t>
+  </si>
+  <si>
+    <t>공기압축기 3호기</t>
+  </si>
+  <si>
+    <t>사출기 1호기</t>
+  </si>
+  <si>
+    <t>사출기 2호기</t>
+  </si>
+  <si>
+    <t>사출기 3호기</t>
+  </si>
+  <si>
+    <t>사출기 4호기</t>
+  </si>
+  <si>
+    <t>장비별 연동 포인트</t>
+  </si>
+  <si>
+    <t>에너지트리 매핑정보</t>
+  </si>
+  <si>
+    <t>설비트리 매핑정보</t>
+  </si>
+  <si>
+    <t>계측기 및 연동장비</t>
+  </si>
+  <si>
+    <t>제품명</t>
+  </si>
+  <si>
+    <t>연동요청</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>FEMS 등록정보</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>포인트정보</t>
+  </si>
+  <si>
+    <t>포인트명</t>
+  </si>
+  <si>
+    <t>계측유형</t>
+  </si>
+  <si>
+    <t>통계유형</t>
+  </si>
+  <si>
+    <t>배율</t>
+  </si>
+  <si>
+    <t>Func Code</t>
+  </si>
+  <si>
+    <t>Point Type</t>
+  </si>
+  <si>
+    <t>Point Size</t>
+  </si>
+  <si>
+    <t>사용량</t>
+  </si>
+  <si>
+    <t>전력</t>
+  </si>
+  <si>
+    <t>전류</t>
+  </si>
+  <si>
+    <t>전압</t>
+  </si>
+  <si>
+    <t>무효전력</t>
+  </si>
+  <si>
+    <t>역률</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>Unbalance</t>
+  </si>
+  <si>
+    <t>에너지</t>
+  </si>
+  <si>
+    <t>가동시간</t>
+  </si>
+  <si>
+    <t>효율</t>
+  </si>
+  <si>
+    <t>11106</t>
+  </si>
+  <si>
+    <t>삼상의 상전압 평균</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>상전압</t>
+  </si>
+  <si>
+    <t>측정값</t>
+  </si>
+  <si>
+    <t>평균</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>11200+(150*x)+6</t>
+  </si>
+  <si>
+    <t>삼상전류 평균</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>11200+(150*x)+66</t>
+  </si>
+  <si>
+    <t>삼상의 유효전력 총합</t>
+  </si>
+  <si>
+    <t>유효전력</t>
+  </si>
+  <si>
+    <t>11200+(150*x)+74</t>
+  </si>
+  <si>
+    <t>삼상의 무효전력 총합</t>
+  </si>
+  <si>
+    <t>kVAR</t>
+  </si>
+  <si>
+    <t>11200+(150*x)+92</t>
+  </si>
+  <si>
+    <t>삼상의 수전한 유효전력량</t>
+  </si>
+  <si>
+    <t>유효전력량</t>
+  </si>
+  <si>
+    <t>변화값</t>
+  </si>
+  <si>
+    <t>합산</t>
+  </si>
+  <si>
+    <t>11200+(150*x)+130</t>
+  </si>
+  <si>
+    <t>Total 역률</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Total 유효전력</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>평균 역률</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>상전압 평균</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>상전류 평균</t>
+  </si>
+  <si>
+    <t>설비코드규칙</t>
+  </si>
+  <si>
+    <t>에너지원 코드규칙</t>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>장비타입</t>
+  </si>
+  <si>
+    <t>펌프</t>
+  </si>
+  <si>
+    <t>입력코드</t>
   </si>
   <si>
     <t>에너지원</t>
-  </si>
-  <si>
-    <t>전기</t>
-  </si>
-  <si>
-    <t>가스</t>
-  </si>
-  <si>
-    <t>건물규모</t>
-  </si>
-  <si>
-    <t>동</t>
-  </si>
-  <si>
-    <t>존</t>
-  </si>
-  <si>
-    <t>층</t>
-  </si>
-  <si>
-    <t>연면적</t>
-  </si>
-  <si>
-    <t>준공년도</t>
-  </si>
-  <si>
-    <t>년</t>
-  </si>
-  <si>
-    <t>상주인력</t>
-  </si>
-  <si>
-    <t>연편균 에너지 사용량</t>
-  </si>
-  <si>
-    <t>일 평균 운영시간</t>
-  </si>
-  <si>
-    <t>FEMS 설정</t>
-  </si>
-  <si>
-    <t>*요금 적용 전력</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>*수전용량</t>
-  </si>
-  <si>
-    <t>에너지 정보</t>
-  </si>
-  <si>
-    <t>종류</t>
-  </si>
-  <si>
-    <t>에너지원 기본 단위</t>
-  </si>
-  <si>
-    <t>kWh</t>
-  </si>
-  <si>
-    <t>탭표시명</t>
-  </si>
-  <si>
-    <t>전력</t>
-  </si>
-  <si>
-    <t>석유환산계수[toe/기본단위]</t>
-  </si>
-  <si>
-    <t>탄소배출계수 [tco2/기본단위]</t>
-  </si>
-  <si>
-    <t>에너지 단가 [원/기본단위]</t>
-  </si>
-  <si>
-    <t>등록 장비 정보</t>
-  </si>
-  <si>
-    <t>*장비ID</t>
-  </si>
-  <si>
-    <t>*장비 타입</t>
-  </si>
-  <si>
-    <t>* 제품명</t>
-  </si>
-  <si>
-    <t>측정설비</t>
-  </si>
-  <si>
-    <t>장비 위치</t>
-  </si>
-  <si>
-    <t>*IP 주소</t>
-  </si>
-  <si>
-    <t>설치 일자</t>
-  </si>
-  <si>
-    <t>프로토콜 타입</t>
-  </si>
-  <si>
-    <t>엔진 ID</t>
-  </si>
-  <si>
-    <t>Offset</t>
-  </si>
-  <si>
-    <t>포트</t>
-  </si>
-  <si>
-    <t>전송주기</t>
-  </si>
-  <si>
-    <t>모니터링 주기</t>
-  </si>
-  <si>
-    <t>전력 채널 수</t>
-  </si>
-  <si>
-    <t>계산 여부</t>
-  </si>
-  <si>
-    <t>사용여부</t>
-  </si>
-  <si>
-    <t>전력량계</t>
-  </si>
-  <si>
-    <t>Accura 2300</t>
-  </si>
-  <si>
-    <t>제1수전 한전메인 배전반</t>
-  </si>
-  <si>
-    <t>1공장 전기실</t>
-  </si>
-  <si>
-    <t>100.100.0.11</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>제2수전 한전메인 배전반</t>
-  </si>
-  <si>
-    <t>2공장 전기실</t>
-  </si>
-  <si>
-    <t>100.100.0.12</t>
-  </si>
-  <si>
-    <t>압출기</t>
-  </si>
-  <si>
-    <t>1공장</t>
-  </si>
-  <si>
-    <t>100.100.0.13</t>
-  </si>
-  <si>
-    <t>MPM330a</t>
-  </si>
-  <si>
-    <t>공압기</t>
-  </si>
-  <si>
-    <t>1공장 유틸리티동</t>
-  </si>
-  <si>
-    <t>100.100.0.14</t>
-  </si>
-  <si>
-    <t>사출기</t>
-  </si>
-  <si>
-    <t>2공장</t>
-  </si>
-  <si>
-    <t>100.100.0.15</t>
-  </si>
-  <si>
-    <t>채널정보</t>
-  </si>
-  <si>
-    <t>설비 트리 연동</t>
-  </si>
-  <si>
-    <t>측정부하명</t>
-  </si>
-  <si>
-    <t>설비코드정보</t>
-  </si>
-  <si>
-    <t>설비그룹명</t>
-  </si>
-  <si>
-    <t>설비그룹ID</t>
-  </si>
-  <si>
-    <t>설비명</t>
-  </si>
-  <si>
-    <t>설비ID</t>
-  </si>
-  <si>
-    <t>제1수전 한전메인</t>
-  </si>
-  <si>
-    <t>수배전반</t>
-  </si>
-  <si>
-    <t>제1수전 메인</t>
-  </si>
-  <si>
-    <t>제2수전 한전메인</t>
-  </si>
-  <si>
-    <t>제2수전 메인</t>
-  </si>
-  <si>
-    <t>압출기1호</t>
-  </si>
-  <si>
-    <t>압출기2호</t>
-  </si>
-  <si>
-    <t>압출기 1~2호 통합</t>
-  </si>
-  <si>
-    <t>공압기1호</t>
-  </si>
-  <si>
-    <t>공기압축기</t>
-  </si>
-  <si>
-    <t>A동 공압기</t>
-  </si>
-  <si>
-    <t>공압기2호</t>
-  </si>
-  <si>
-    <t>공압기3호</t>
-  </si>
-  <si>
-    <t>공압기 1~3호 통합</t>
-  </si>
-  <si>
-    <t>사출기1호</t>
-  </si>
-  <si>
-    <t>사출기2호</t>
-  </si>
-  <si>
-    <t>사출기3호</t>
-  </si>
-  <si>
-    <t>사출기4호</t>
-  </si>
-  <si>
-    <t>사출기 1~4호 통합</t>
-  </si>
-  <si>
-    <t>에너지트리정보</t>
-  </si>
-  <si>
-    <t>에너지 포인트연동</t>
-  </si>
-  <si>
-    <t>*에너지원</t>
-  </si>
-  <si>
-    <t>* 계통명</t>
-  </si>
-  <si>
-    <t>*에너지계통 ID</t>
-  </si>
-  <si>
-    <t>계통레벨</t>
-  </si>
-  <si>
-    <t>연결계통ID</t>
-  </si>
-  <si>
-    <t>장비ID</t>
-  </si>
-  <si>
-    <t>압출기 1호기</t>
-  </si>
-  <si>
-    <t>압출기 2호기</t>
-  </si>
-  <si>
-    <t>공기압축기 1호기</t>
-  </si>
-  <si>
-    <t>공기압축기 2호기</t>
-  </si>
-  <si>
-    <t>공기압축기 3호기</t>
-  </si>
-  <si>
-    <t>사출기 1호기</t>
-  </si>
-  <si>
-    <t>사출기 2호기</t>
-  </si>
-  <si>
-    <t>사출기 3호기</t>
-  </si>
-  <si>
-    <t>사출기 4호기</t>
-  </si>
-  <si>
-    <t>장비별 연동 포인트</t>
-  </si>
-  <si>
-    <t>에너지트리 매핑정보</t>
-  </si>
-  <si>
-    <t>설비트리 매핑정보</t>
-  </si>
-  <si>
-    <t>계측기 및 연동장비</t>
-  </si>
-  <si>
-    <t>제품명</t>
-  </si>
-  <si>
-    <t>연동요청</t>
-  </si>
-  <si>
-    <t>단위</t>
-  </si>
-  <si>
-    <t>FEMS 등록정보</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>포인트정보</t>
-  </si>
-  <si>
-    <t>포인트명</t>
-  </si>
-  <si>
-    <t>계측유형</t>
-  </si>
-  <si>
-    <t>통계유형</t>
-  </si>
-  <si>
-    <t>배율</t>
-  </si>
-  <si>
-    <t>Func Code</t>
-  </si>
-  <si>
-    <t>Point Type</t>
-  </si>
-  <si>
-    <t>Point Size</t>
-  </si>
-  <si>
-    <t>사용량</t>
-  </si>
-  <si>
-    <t>전류</t>
-  </si>
-  <si>
-    <t>전압</t>
-  </si>
-  <si>
-    <t>무효전력</t>
-  </si>
-  <si>
-    <t>역률</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>Unbalance</t>
-  </si>
-  <si>
-    <t>에너지</t>
-  </si>
-  <si>
-    <t>가동시간</t>
-  </si>
-  <si>
-    <t>효율</t>
-  </si>
-  <si>
-    <t>11106</t>
-  </si>
-  <si>
-    <t>삼상의 상전압 평균</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>상전압</t>
-  </si>
-  <si>
-    <t>측정값</t>
-  </si>
-  <si>
-    <t>평균</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>11200+(150*x)+6</t>
-  </si>
-  <si>
-    <t>삼상전류 평균</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>11200+(150*x)+66</t>
-  </si>
-  <si>
-    <t>삼상의 유효전력 총합</t>
-  </si>
-  <si>
-    <t>유효전력</t>
-  </si>
-  <si>
-    <t>11200+(150*x)+74</t>
-  </si>
-  <si>
-    <t>삼상의 무효전력 총합</t>
-  </si>
-  <si>
-    <t>kVAR</t>
-  </si>
-  <si>
-    <t>11200+(150*x)+92</t>
-  </si>
-  <si>
-    <t>삼상의 수전한 유효전력량</t>
-  </si>
-  <si>
-    <t>유효전력량</t>
-  </si>
-  <si>
-    <t>변화값</t>
-  </si>
-  <si>
-    <t>합산</t>
-  </si>
-  <si>
-    <t>11200+(150*x)+130</t>
-  </si>
-  <si>
-    <t>Total 역률</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Total 유효전력</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>평균 역률</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>상전압 평균</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>상전류 평균</t>
-  </si>
-  <si>
-    <t>설비코드규칙</t>
-  </si>
-  <si>
-    <t>에너지원 코드규칙</t>
-  </si>
-  <si>
-    <t>구분</t>
-  </si>
-  <si>
-    <t>장비타입</t>
-  </si>
-  <si>
-    <t>펌프</t>
-  </si>
-  <si>
-    <t>입력코드</t>
   </si>
   <si>
     <t>팬</t>
@@ -1217,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1225,283 +1129,168 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C10" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>2400</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>26</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C18">
+        <v>3000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>12800</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20">
-        <v>2011</v>
-      </c>
-      <c r="G20" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21">
-        <v>145</v>
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22">
-        <v>1820</v>
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C23">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
+        <v>0.00023</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C24">
-        <v>2400</v>
-      </c>
-      <c r="G24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+        <v>0.0004594</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C25">
-        <v>3000</v>
-      </c>
-      <c r="G25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30">
-        <v>0.00023</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31">
-        <v>0.0004594</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32">
         <v>148.5</v>
       </c>
     </row>
@@ -1513,312 +1302,204 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>66</v>
+        <v>42</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G3" s="2">
+        <v>49</v>
+      </c>
+      <c r="F3">
+        <v>502</v>
+      </c>
+      <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2">
         <v>45034.38888888889</v>
       </c>
-      <c r="I3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>502</v>
-      </c>
-      <c r="M3">
-        <v>15</v>
-      </c>
-      <c r="N3">
-        <v>15</v>
-      </c>
-      <c r="O3">
-        <v>40</v>
-      </c>
-      <c r="P3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="2">
+        <v>52</v>
+      </c>
+      <c r="F4">
+        <v>502</v>
+      </c>
+      <c r="G4">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2">
         <v>45034.38888888889</v>
       </c>
-      <c r="I4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="J4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5">
         <v>502</v>
       </c>
-      <c r="M4">
+      <c r="G5">
+        <v>40</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="N4">
+      <c r="I5" s="2">
+        <v>45034.38888888889</v>
+      </c>
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6">
+        <v>502</v>
+      </c>
+      <c r="G6">
+        <v>40</v>
+      </c>
+      <c r="H6">
         <v>15</v>
       </c>
-      <c r="O4">
-        <v>40</v>
-      </c>
-      <c r="P4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="I6" s="2">
         <v>45034.38888888889</v>
       </c>
-      <c r="I5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>502</v>
-      </c>
-      <c r="M5">
-        <v>15</v>
-      </c>
-      <c r="N5">
-        <v>15</v>
-      </c>
-      <c r="O5">
-        <v>40</v>
-      </c>
-      <c r="P5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="2">
-        <v>45034.38888888889</v>
-      </c>
-      <c r="I6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>502</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-      <c r="N6">
-        <v>15</v>
-      </c>
-      <c r="O6">
-        <v>40</v>
-      </c>
-      <c r="P6" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G7" s="2">
+        <v>59</v>
+      </c>
+      <c r="F7">
+        <v>502</v>
+      </c>
+      <c r="G7">
+        <v>40</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2">
         <v>45034.38888888889</v>
       </c>
-      <c r="I7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>502</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-      <c r="N7">
-        <v>15</v>
-      </c>
-      <c r="O7">
-        <v>40</v>
-      </c>
-      <c r="P7" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>82</v>
+      <c r="J7" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1834,36 +1515,36 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1874,19 +1555,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1900,19 +1581,19 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -1926,19 +1607,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1952,19 +1633,19 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1978,7 +1659,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1989,19 +1670,19 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2015,19 +1696,19 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -2041,19 +1722,19 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -2067,7 +1748,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2078,19 +1759,19 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F12">
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2104,19 +1785,19 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -2130,19 +1811,19 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F14">
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -2156,19 +1837,19 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F15">
         <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="H15">
         <v>4</v>
@@ -2182,7 +1863,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2198,33 +1879,33 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="F1" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2232,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2255,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -2278,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2301,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2324,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -2347,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -2370,7 +2051,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -2393,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -2416,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -2439,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -2462,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="C13">
         <v>11</v>
@@ -2485,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -2508,7 +2189,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -2531,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -2562,118 +2243,118 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="M1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="U1" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="H3" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="I3" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="K3" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="L3" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="M3" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="N3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="O3" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="P3" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="Q3" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="R3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="S3" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="T3" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="U3" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="V3" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="W3" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2688,27 +2369,27 @@
         <v>4</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H5" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2723,27 +2404,27 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="G6" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H6" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2758,27 +2439,27 @@
         <v>4</v>
       </c>
       <c r="N6" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="G7" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2793,27 +2474,27 @@
         <v>4</v>
       </c>
       <c r="Q7" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="H8" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2828,30 +2509,30 @@
         <v>4</v>
       </c>
       <c r="M8" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="U8" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="F9" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -2866,33 +2547,33 @@
         <v>4</v>
       </c>
       <c r="R9" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H10" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I10">
         <v>0.001</v>
@@ -2907,27 +2588,27 @@
         <v>4</v>
       </c>
       <c r="N10" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="F11" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="G11" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H11" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I11">
         <v>0.01</v>
@@ -2942,27 +2623,27 @@
         <v>4</v>
       </c>
       <c r="R11" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2977,30 +2658,30 @@
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="U12" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="F13" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I13">
         <v>0.01</v>
@@ -3015,27 +2696,27 @@
         <v>4</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="F14" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="G14" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H14" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="I14">
         <v>0.001</v>
@@ -3050,7 +2731,7 @@
         <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -3066,222 +2747,222 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="E1" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="F3" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="F10">
         <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="F12">
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3297,182 +2978,182 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
